--- a/Makhana_Dataset_Grade_3.xlsx
+++ b/Makhana_Dataset_Grade_3.xlsx
@@ -1,24 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CSIO\makhana work_july2026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC7AE72-1F32-4AA6-BB03-67C25FDF83C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="28695" windowHeight="12540" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grade 3" sheetId="1" r:id="rId1"/>
     <sheet name="Grade 4" sheetId="2" r:id="rId2"/>
     <sheet name="Grade 5" sheetId="3" r:id="rId3"/>
-    <sheet name="Grade 6_1" sheetId="4" r:id="rId4"/>
-    <sheet name="Grade 6_2(correct)" sheetId="6" r:id="rId5"/>
+    <sheet name="Grade 6" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="35">
   <si>
     <t>Kernel ID</t>
   </si>
@@ -118,12 +134,18 @@
   <si>
     <t xml:space="preserve">        Mean</t>
   </si>
+  <si>
+    <t>difference</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,24 +168,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -178,31 +188,228 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -240,7 +447,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -274,6 +481,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -308,9 +516,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -483,21 +692,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="21" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="14.42578125" style="1"/>
-    <col min="3" max="3" width="26.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="21.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="14.42578125" style="1"/>
+    <col min="1" max="2" width="14.44140625" style="1"/>
+    <col min="3" max="3" width="26.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" style="1" customWidth="1"/>
+    <col min="6" max="8" width="21.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="14.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,19 +729,22 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -552,8 +764,27 @@
         <f>AVERAGE(C2:E2)</f>
         <v>16.253333333333334</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="G2" s="2">
+        <v>14.96108205776428</v>
+      </c>
+      <c r="H2" s="2">
+        <f>F2-G2</f>
+        <v>1.2922512755690541</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.82209827425637672</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.69639745543528886</v>
+      </c>
+      <c r="K2" s="2">
+        <v>66.64244067073821</v>
+      </c>
+      <c r="L2" s="2">
+        <v>44.962103599874503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -570,11 +801,30 @@
         <v>13.15</v>
       </c>
       <c r="F3" s="2">
-        <f>AVERAGE(C3:E3)</f>
+        <f t="shared" ref="F3:F21" si="0">AVERAGE(C3:E3)</f>
         <v>12.833333333333334</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="G3" s="2">
+        <v>12.794509573763049</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H21" si="1">F3-G3</f>
+        <v>3.8823759570284722E-2</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.91168138638774532</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.85996793534687732</v>
+      </c>
+      <c r="K3" s="2">
+        <v>70.824478602014807</v>
+      </c>
+      <c r="L3" s="2">
+        <v>47.628696796401641</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -591,11 +841,30 @@
         <v>12.84</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F21" si="0">AVERAGE(C4:E4)</f>
+        <f t="shared" si="0"/>
         <v>12.786666666666667</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="G4" s="2">
+        <v>12.996826360112239</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.21015969344557206</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.93920576870014305</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.84446954116494666</v>
+      </c>
+      <c r="K4" s="2">
+        <v>73.852137130633125</v>
+      </c>
+      <c r="L4" s="2">
+        <v>49.816495547109866</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -615,8 +884,27 @@
         <f t="shared" si="0"/>
         <v>12.983333333333334</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="G5" s="2">
+        <v>12.794509573763049</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="1"/>
+        <v>0.18882375957028508</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.90782995623778195</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.92754225262317935</v>
+      </c>
+      <c r="K5" s="2">
+        <v>73.643809079475844</v>
+      </c>
+      <c r="L5" s="2">
+        <v>47.229169112754882</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -636,8 +924,27 @@
         <f t="shared" si="0"/>
         <v>11.723333333333334</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="G6" s="2">
+        <v>10.924573379215509</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>0.79875995411782519</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.35283657976262328</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.7654867539039989</v>
+      </c>
+      <c r="K6" s="2">
+        <v>50.50543579339427</v>
+      </c>
+      <c r="L6" s="2">
+        <v>41.629769274535278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -657,8 +964,27 @@
         <f t="shared" si="0"/>
         <v>16.066666666666666</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="G7" s="2">
+        <v>14.92808237022531</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="1"/>
+        <v>1.1385842964413566</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.588981492238279</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.694126431492051</v>
+      </c>
+      <c r="K7" s="2">
+        <v>67.029601265427772</v>
+      </c>
+      <c r="L7" s="2">
+        <v>46.221095857199131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -678,8 +1004,27 @@
         <f t="shared" si="0"/>
         <v>13.829999999999998</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="G8" s="2">
+        <v>13.208091747115731</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>0.62190825288426765</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.61255856416610921</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.74863959163959259</v>
+      </c>
+      <c r="K8" s="2">
+        <v>60.052318979823568</v>
+      </c>
+      <c r="L8" s="2">
+        <v>41.152847929132022</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -699,8 +1044,27 @@
         <f t="shared" si="0"/>
         <v>12.72</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="G9" s="2">
+        <v>12.99988609280056</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.27988609280055954</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.96296024697959426</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.88851991710791001</v>
+      </c>
+      <c r="K9" s="2">
+        <v>74.240502763103493</v>
+      </c>
+      <c r="L9" s="2">
+        <v>55.228083066039289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -720,8 +1084,27 @@
         <f t="shared" si="0"/>
         <v>12.173333333333332</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="G10" s="2">
+        <v>12.949615182519549</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.77628184918621734</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.95905142890269823</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.90224248629653314</v>
+      </c>
+      <c r="K10" s="2">
+        <v>72.506008173941055</v>
+      </c>
+      <c r="L10" s="2">
+        <v>48.963392917304382</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -741,8 +1124,27 @@
         <f t="shared" si="0"/>
         <v>12.209999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="G11" s="2">
+        <v>13.20267057138974</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.99267057138974124</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.96495288061802309</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.90787928759894454</v>
+      </c>
+      <c r="K11" s="2">
+        <v>79.636362224558823</v>
+      </c>
+      <c r="L11" s="2">
+        <v>50.022712125995298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -762,8 +1164,27 @@
         <f t="shared" si="0"/>
         <v>11.986666666666665</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="G12" s="2">
+        <v>11.995552113335309</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="1"/>
+        <v>-8.8854466686445477E-3</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.85341113944494307</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.87275002781900313</v>
+      </c>
+      <c r="K12" s="2">
+        <v>69.86057249808465</v>
+      </c>
+      <c r="L12" s="2">
+        <v>45.613061168195287</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -783,8 +1204,27 @@
         <f t="shared" si="0"/>
         <v>12.530000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="G13" s="2">
+        <v>12.48871076290424</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>4.1289237095760711E-2</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.68757425266601446</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.89529549209779802</v>
+      </c>
+      <c r="K13" s="2">
+        <v>64.035881242835387</v>
+      </c>
+      <c r="L13" s="2">
+        <v>48.461903406395287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -804,8 +1244,27 @@
         <f t="shared" si="0"/>
         <v>13.256666666666668</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="G14" s="2">
+        <v>13.04996335152854</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>0.20670331513812812</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.6784226978402832</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.80034480891531634</v>
+      </c>
+      <c r="K14" s="2">
+        <v>69.259946404162179</v>
+      </c>
+      <c r="L14" s="2">
+        <v>46.396845588844528</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -825,8 +1284,27 @@
         <f t="shared" si="0"/>
         <v>11.966666666666667</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="G15" s="2">
+        <v>12.071568220161231</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.10490155349456387</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.79238671070817324</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.75840466321243527</v>
+      </c>
+      <c r="K15" s="2">
+        <v>72.632274549186548</v>
+      </c>
+      <c r="L15" s="2">
+        <v>50.327499778191822</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -846,8 +1324,27 @@
         <f t="shared" si="0"/>
         <v>13.086666666666666</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="2">
+        <v>13.792571079788511</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.7059044131218446</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.92114574846671027</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.93650107915982583</v>
+      </c>
+      <c r="K16" s="2">
+        <v>79.079365982573975</v>
+      </c>
+      <c r="L16" s="2">
+        <v>53.082943232814408</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -867,8 +1364,27 @@
         <f t="shared" si="0"/>
         <v>12.353333333333333</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="2">
+        <v>12.49125817971052</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.13792484637718694</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.82166633146678425</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.9166347375151882</v>
+      </c>
+      <c r="K17" s="2">
+        <v>72.365091693605223</v>
+      </c>
+      <c r="L17" s="2">
+        <v>47.704356491140658</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -888,8 +1404,27 @@
         <f t="shared" si="0"/>
         <v>10.873333333333333</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="2">
+        <v>11.66610720837952</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.79277387504618702</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.8941068498974164</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.91229361301078782</v>
+      </c>
+      <c r="K18" s="2">
+        <v>71.192162816509381</v>
+      </c>
+      <c r="L18" s="2">
+        <v>51.621043267092247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -909,8 +1444,27 @@
         <f t="shared" si="0"/>
         <v>11.663333333333334</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="2">
+        <v>12.54463443704064</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.88130110370730641</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.85179946319068334</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.87396363849317849</v>
+      </c>
+      <c r="K19" s="2">
+        <v>74.331691592831206</v>
+      </c>
+      <c r="L19" s="2">
+        <v>50.010224017330223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -930,8 +1484,27 @@
         <f t="shared" si="0"/>
         <v>10.993333333333334</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="2">
+        <v>12.27413641478002</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.2808030814466864</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.99433926334633349</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.97452102089316539</v>
+      </c>
+      <c r="K20" s="2">
+        <v>76.233202629656674</v>
+      </c>
+      <c r="L20" s="2">
+        <v>51.835552499426967</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -951,31 +1524,59 @@
         <f t="shared" si="0"/>
         <v>14.166666666666666</v>
       </c>
+      <c r="G21" s="2">
+        <v>14.268785493482889</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.10211882681622342</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.89792441660965971</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.84748647303685087</v>
+      </c>
+      <c r="K21" s="2">
+        <v>79.995060047102641</v>
+      </c>
+      <c r="L21" s="2">
+        <v>49.347003484841693</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H2:H21">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="lessThan">
+      <formula>-0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
-    <col min="3" max="3" width="25.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" customWidth="1"/>
     <col min="5" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -998,19 +1599,22 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21">
+    <row r="2" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1027,16 +1631,30 @@
         <v>19.850000000000001</v>
       </c>
       <c r="F2" s="2">
-        <f>AVERAGE(C2:E3)</f>
-        <v>19.954999999999998</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="21">
+        <f>AVERAGE(C2:E2)</f>
+        <v>19.566666666666666</v>
+      </c>
+      <c r="G2" s="2">
+        <v>19.499115272525</v>
+      </c>
+      <c r="H2" s="2">
+        <f>F2-G2</f>
+        <v>6.7551394141666776E-2</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.92664786993619785</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.89662445626992826</v>
+      </c>
+      <c r="K2" s="2">
+        <v>92.109182082946816</v>
+      </c>
+      <c r="L2" s="2">
+        <v>46.441290426931928</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1053,16 +1671,30 @@
         <v>21.15</v>
       </c>
       <c r="F3" s="2">
-        <f t="shared" ref="F3:F21" si="0">AVERAGE(C3:E4)</f>
-        <v>19.978333333333335</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="21">
+        <f t="shared" ref="F3:F21" si="0">AVERAGE(C3:E3)</f>
+        <v>20.34333333333333</v>
+      </c>
+      <c r="G3" s="2">
+        <v>20.997401978703241</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H21" si="1">F3-G3</f>
+        <v>-0.65406864536991094</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.96936803875199318</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.95271378462408807</v>
+      </c>
+      <c r="K3" s="2">
+        <v>90.55157706587562</v>
+      </c>
+      <c r="L3" s="2">
+        <v>47.853078629560727</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,15 +1712,29 @@
       </c>
       <c r="F4" s="2">
         <f t="shared" si="0"/>
-        <v>21.51</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="21">
+        <v>19.613333333333333</v>
+      </c>
+      <c r="G4" s="2">
+        <v>19.952760945780021</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.33942761244668773</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.87934639447755569</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.89866210723146189</v>
+      </c>
+      <c r="K4" s="2">
+        <v>93.495648359119684</v>
+      </c>
+      <c r="L4" s="2">
+        <v>50.678240220886373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1106,15 +1752,29 @@
       </c>
       <c r="F5" s="2">
         <f t="shared" si="0"/>
-        <v>20.631666666666671</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="21">
+        <v>23.406666666666666</v>
+      </c>
+      <c r="G5" s="2">
+        <v>22.404198036428621</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0024686302380452</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.87607498459763844</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.8712246587401149</v>
+      </c>
+      <c r="K5" s="2">
+        <v>91.758126516978564</v>
+      </c>
+      <c r="L5" s="2">
+        <v>50.913374658468527</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1132,15 +1792,29 @@
       </c>
       <c r="F6" s="2">
         <f t="shared" si="0"/>
-        <v>18.056666666666668</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="21">
+        <v>17.856666666666666</v>
+      </c>
+      <c r="G6" s="2">
+        <v>17.22623237335106</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>0.63043429331560574</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.8951529002097427</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.82554388294755021</v>
+      </c>
+      <c r="K6" s="2">
+        <v>77.904647373870802</v>
+      </c>
+      <c r="L6" s="2">
+        <v>45.740368691824102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1158,15 +1832,29 @@
       </c>
       <c r="F7" s="2">
         <f t="shared" si="0"/>
-        <v>19.946666666666669</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="21">
+        <v>18.256666666666664</v>
+      </c>
+      <c r="G7" s="2">
+        <v>17.497001551775181</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="1"/>
+        <v>0.75966511489148303</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.85493111447739467</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.8466165601851755</v>
+      </c>
+      <c r="K7" s="2">
+        <v>91.280034363338601</v>
+      </c>
+      <c r="L7" s="2">
+        <v>51.096898529526747</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1184,15 +1872,29 @@
       </c>
       <c r="F8" s="2">
         <f t="shared" si="0"/>
-        <v>21.044999999999998</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="21">
+        <v>21.636666666666667</v>
+      </c>
+      <c r="G8" s="2">
+        <v>21.330398679803551</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>0.30626798686311574</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.89935698197996927</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.81927015729162378</v>
+      </c>
+      <c r="K8" s="2">
+        <v>94.44648146803118</v>
+      </c>
+      <c r="L8" s="2">
+        <v>52.225707321280247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1210,15 +1912,29 @@
       </c>
       <c r="F9" s="2">
         <f t="shared" si="0"/>
-        <v>19.526666666666667</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="21">
+        <v>20.453333333333333</v>
+      </c>
+      <c r="G9" s="2">
+        <v>21.440495630920491</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.98716229758715812</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.89083111989567265</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.86718677765503094</v>
+      </c>
+      <c r="K9" s="2">
+        <v>95.011842893004683</v>
+      </c>
+      <c r="L9" s="2">
+        <v>57.04816579494161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1236,15 +1952,29 @@
       </c>
       <c r="F10" s="2">
         <f t="shared" si="0"/>
-        <v>17.686666666666664</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="21">
+        <v>18.599999999999998</v>
+      </c>
+      <c r="G10" s="2">
+        <v>18.212475723355212</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>0.38752427664478617</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.69161752774413532</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.87857762774635562</v>
+      </c>
+      <c r="K10" s="2">
+        <v>89.371268573719917</v>
+      </c>
+      <c r="L10" s="2">
+        <v>51.233726349247263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1262,15 +1992,29 @@
       </c>
       <c r="F11" s="2">
         <f t="shared" si="0"/>
-        <v>17.889999999999997</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="21">
+        <v>16.77333333333333</v>
+      </c>
+      <c r="G11" s="2">
+        <v>17.184624172347501</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.41129083901417118</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.96972339021678844</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.88770856916431129</v>
+      </c>
+      <c r="K11" s="2">
+        <v>92.635571401763926</v>
+      </c>
+      <c r="L11" s="2">
+        <v>49.69400418395206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1288,15 +2032,29 @@
       </c>
       <c r="F12" s="2">
         <f t="shared" si="0"/>
-        <v>19.573333333333334</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="21">
+        <v>19.006666666666664</v>
+      </c>
+      <c r="G12" s="2">
+        <v>19.673339447811301</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.66667278114463713</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.9629298106741131</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.91999194523037964</v>
+      </c>
+      <c r="K12" s="2">
+        <v>94.254816001615325</v>
+      </c>
+      <c r="L12" s="2">
+        <v>56.213130589447189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -1314,15 +2072,29 @@
       </c>
       <c r="F13" s="2">
         <f t="shared" si="0"/>
-        <v>18.731666666666669</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="21">
+        <v>20.14</v>
+      </c>
+      <c r="G13" s="2">
+        <v>20.805216840404931</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.66521684040493057</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.95495118232446818</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.89651598522559373</v>
+      </c>
+      <c r="K13" s="2">
+        <v>95.427416209127742</v>
+      </c>
+      <c r="L13" s="2">
+        <v>63.111638203668562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -1340,15 +2112,29 @@
       </c>
       <c r="F14" s="2">
         <f t="shared" si="0"/>
-        <v>17.618333333333336</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="21">
+        <v>17.323333333333334</v>
+      </c>
+      <c r="G14" s="2">
+        <v>17.70803147306637</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.38469813973303602</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.90186628075177266</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.86711781328373039</v>
+      </c>
+      <c r="K14" s="2">
+        <v>93.4533435440745</v>
+      </c>
+      <c r="L14" s="2">
+        <v>60.144539460424397</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1366,15 +2152,29 @@
       </c>
       <c r="F15" s="2">
         <f t="shared" si="0"/>
-        <v>17.010000000000002</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="21">
+        <v>17.913333333333334</v>
+      </c>
+      <c r="G15" s="2">
+        <v>18.62874554594757</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.71541221261423615</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.97812624977295692</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.89665339982678383</v>
+      </c>
+      <c r="K15" s="2">
+        <v>92.174275651898299</v>
+      </c>
+      <c r="L15" s="2">
+        <v>60.461289919707347</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1392,15 +2192,29 @@
       </c>
       <c r="F16" s="2">
         <f t="shared" si="0"/>
-        <v>16.736666666666668</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="21">
+        <v>16.106666666666666</v>
+      </c>
+      <c r="G16" s="2">
+        <v>17.033993135367311</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.92732646870064528</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.94772806325962611</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.87954929257873127</v>
+      </c>
+      <c r="K16" s="2">
+        <v>74.010711147663983</v>
+      </c>
+      <c r="L16" s="2">
+        <v>49.524418887621977</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -1418,15 +2232,29 @@
       </c>
       <c r="F17" s="2">
         <f t="shared" si="0"/>
-        <v>20.468333333333334</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="21">
+        <v>17.366666666666667</v>
+      </c>
+      <c r="G17" s="2">
+        <v>16.487756840605471</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="1"/>
+        <v>0.8789098260611965</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.91046635671257958</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.83275192880942484</v>
+      </c>
+      <c r="K17" s="2">
+        <v>90.29356135134482</v>
+      </c>
+      <c r="L17" s="2">
+        <v>55.482319557245617</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1444,15 +2272,29 @@
       </c>
       <c r="F18" s="2">
         <f t="shared" si="0"/>
-        <v>19.905000000000005</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="21">
+        <v>23.570000000000004</v>
+      </c>
+      <c r="G18" s="2">
+        <v>24.133580087274989</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.56358008727498543</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.89173150496989484</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.88200817804639331</v>
+      </c>
+      <c r="K18" s="2">
+        <v>97.143469533402921</v>
+      </c>
+      <c r="L18" s="2">
+        <v>59.233231663035582</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -1470,15 +2312,29 @@
       </c>
       <c r="F19" s="2">
         <f t="shared" si="0"/>
-        <v>18.273333333333333</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="21">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="G19" s="2">
+        <v>16.78420258767683</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.54420258767683194</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.94164826935490042</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.94136625786559769</v>
+      </c>
+      <c r="K19" s="2">
+        <v>92.141927599418693</v>
+      </c>
+      <c r="L19" s="2">
+        <v>62.322503636838377</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1496,15 +2352,29 @@
       </c>
       <c r="F20" s="2">
         <f t="shared" si="0"/>
-        <v>18.02</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" ht="21">
+        <v>20.306666666666668</v>
+      </c>
+      <c r="G20" s="2">
+        <v>19.109732366904229</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="1"/>
+        <v>1.1969342997624395</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.89803664071811407</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.85945085828954204</v>
+      </c>
+      <c r="K20" s="2">
+        <v>95.305180699387535</v>
+      </c>
+      <c r="L20" s="2">
+        <v>58.024181879000402</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -1524,34 +2394,61 @@
         <f t="shared" si="0"/>
         <v>15.733333333333334</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="G21" s="2">
+        <v>15.630874920813101</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="1"/>
+        <v>0.10245841252023347</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.90661513451270781</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.8804849525301871</v>
+      </c>
+      <c r="K21" s="2">
+        <v>89.648278515120765</v>
+      </c>
+      <c r="L21" s="2">
+        <v>54.661661153601592</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H3:H21">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H21">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="lessThan">
+      <formula>-0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="6" width="25.85546875" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="27.5546875" customWidth="1"/>
+    <col min="5" max="6" width="25.88671875" customWidth="1"/>
+    <col min="7" max="8" width="23.44140625" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1574,19 +2471,22 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21">
+    <row r="2" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1606,13 +2506,27 @@
         <f>AVERAGE(C2:E2)</f>
         <v>22.536666666666665</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="21">
+      <c r="G2" s="2">
+        <v>22.572562601250759</v>
+      </c>
+      <c r="H2" s="2">
+        <f>F2-G2</f>
+        <v>-3.5895934584093681E-2</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.95578112461145059</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.93355742148194309</v>
+      </c>
+      <c r="K2" s="2">
+        <v>95.042770677897309</v>
+      </c>
+      <c r="L2" s="2">
+        <v>49.172548212534657</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1632,13 +2546,27 @@
         <f t="shared" ref="F3:F21" si="0">AVERAGE(C3:E3)</f>
         <v>21.903333333333336</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="21">
+      <c r="G3" s="2">
+        <v>21.00989941896594</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H21" si="1">F3-G3</f>
+        <v>0.89343391436739594</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.91431125540733504</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.85921915974775964</v>
+      </c>
+      <c r="K3" s="2">
+        <v>91</v>
+      </c>
+      <c r="L3" s="2">
+        <v>50.199836919823163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1658,13 +2586,27 @@
         <f t="shared" si="0"/>
         <v>20.52</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="21">
+      <c r="G4" s="2">
+        <v>20.13767802179671</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="1"/>
+        <v>0.38232197820329006</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.84229816500218235</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.83324835098426486</v>
+      </c>
+      <c r="K4" s="2">
+        <v>81.070928749341959</v>
+      </c>
+      <c r="L4" s="2">
+        <v>49.260584641942927</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1684,13 +2626,27 @@
         <f t="shared" si="0"/>
         <v>22.263333333333332</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="21">
+      <c r="G5" s="2">
+        <v>22.210576778774449</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="1"/>
+        <v>5.275655455888284E-2</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.8780169269710365</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.87897766950766831</v>
+      </c>
+      <c r="K5" s="2">
+        <v>94.91399008955662</v>
+      </c>
+      <c r="L5" s="2">
+        <v>51.686001869533293</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1710,13 +2666,27 @@
         <f t="shared" si="0"/>
         <v>23.83666666666667</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="21">
+      <c r="G6" s="2">
+        <v>22.61375440686486</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>1.2229122598018094</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.74110805387845957</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.9380086727847734</v>
+      </c>
+      <c r="K6" s="2">
+        <v>93.094615546815902</v>
+      </c>
+      <c r="L6" s="2">
+        <v>49.19599837720709</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1736,13 +2706,27 @@
         <f t="shared" si="0"/>
         <v>19.386666666666667</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="21">
+      <c r="G7" s="2">
+        <v>19.717360934719789</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.33069426805312219</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.99670826152020997</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.91887501865265453</v>
+      </c>
+      <c r="K7" s="2">
+        <v>90.11566121183121</v>
+      </c>
+      <c r="L7" s="2">
+        <v>52.541776316986791</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1762,13 +2746,27 @@
         <f t="shared" si="0"/>
         <v>21.29</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="21">
+      <c r="G8" s="2">
+        <v>20.83196221311384</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>0.45803778688615893</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.88764894989124743</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.8806691949340455</v>
+      </c>
+      <c r="K8" s="2">
+        <v>93.407362004425281</v>
+      </c>
+      <c r="L8" s="2">
+        <v>56.640621881132937</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1788,13 +2786,27 @@
         <f t="shared" si="0"/>
         <v>22.646666666666665</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="21">
+      <c r="G9" s="2">
+        <v>23.107492057469798</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.46082539080313367</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.94942352931040519</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.87578796079660715</v>
+      </c>
+      <c r="K9" s="2">
+        <v>92.573827814105755</v>
+      </c>
+      <c r="L9" s="2">
+        <v>53.429608246778358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1814,13 +2826,27 @@
         <f t="shared" si="0"/>
         <v>21.406666666666666</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="21">
+      <c r="G10" s="2">
+        <v>22.08379463972701</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.67712797306034389</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.95864602562241397</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.96604207672046749</v>
+      </c>
+      <c r="K10" s="2">
+        <v>95.446661993744613</v>
+      </c>
+      <c r="L10" s="2">
+        <v>53.410850430424617</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1840,13 +2866,27 @@
         <f t="shared" si="0"/>
         <v>23.16</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="21">
+      <c r="G11" s="2">
+        <v>23.23724680973703</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="1"/>
+        <v>-7.724680973703002E-2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.91517753657735645</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.85140589355541485</v>
+      </c>
+      <c r="K11" s="2">
+        <v>94.241244126120122</v>
+      </c>
+      <c r="L11" s="2">
+        <v>48.689534197399126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1866,13 +2906,27 @@
         <f t="shared" si="0"/>
         <v>18.936666666666667</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="21">
+      <c r="G12" s="2">
+        <v>18.704170189902811</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="1"/>
+        <v>0.23249647676385621</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.95791852695500235</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.9795775281160356</v>
+      </c>
+      <c r="K12" s="2">
+        <v>82.643324985222819</v>
+      </c>
+      <c r="L12" s="2">
+        <v>52.877773100131407</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -1892,13 +2946,27 @@
         <f t="shared" si="0"/>
         <v>22.353333333333335</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="21">
+      <c r="G13" s="2">
+        <v>22.319539495463971</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>3.3793837869364296E-2</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.79788828232233544</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.81294108955892108</v>
+      </c>
+      <c r="K13" s="2">
+        <v>94.365599453353454</v>
+      </c>
+      <c r="L13" s="2">
+        <v>57.702042097606373</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -1918,13 +2986,27 @@
         <f t="shared" si="0"/>
         <v>21.189999999999998</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="21">
+      <c r="G14" s="2">
+        <v>22.52070199739525</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.3307019973952521</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.98040854888048934</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.94665834433196405</v>
+      </c>
+      <c r="K14" s="2">
+        <v>89.959075347022917</v>
+      </c>
+      <c r="L14" s="2">
+        <v>54.259410984405129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1944,13 +3026,27 @@
         <f t="shared" si="0"/>
         <v>17.533333333333331</v>
       </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="21">
+      <c r="G15" s="2">
+        <v>17.660352976212899</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.12701964287956713</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.95408816561639276</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.8746594264202372</v>
+      </c>
+      <c r="K15" s="2">
+        <v>91.529120128889659</v>
+      </c>
+      <c r="L15" s="2">
+        <v>56.383392222169682</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1970,13 +3066,27 @@
         <f t="shared" si="0"/>
         <v>20.543333333333333</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="21">
+      <c r="G16" s="2">
+        <v>20.32012956807392</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>0.22320376525941299</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.93706514599666191</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.87783183338492632</v>
+      </c>
+      <c r="K16" s="2">
+        <v>86.867335125190323</v>
+      </c>
+      <c r="L16" s="2">
+        <v>51.762222105612977</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,13 +3106,27 @@
         <f t="shared" si="0"/>
         <v>20.319999999999997</v>
       </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="21">
+      <c r="G17" s="2">
+        <v>20.402948033964769</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="1"/>
+        <v>-8.294803396477235E-2</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.93852596266681199</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.91738756668315791</v>
+      </c>
+      <c r="K17" s="2">
+        <v>94.221008380240619</v>
+      </c>
+      <c r="L17" s="2">
+        <v>52.013573386089263</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -2022,13 +3146,27 @@
         <f t="shared" si="0"/>
         <v>20.733333333333334</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="21">
+      <c r="G18" s="2">
+        <v>21.67332873253908</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.93999539920574549</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.93213846664713929</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.94973637892727403</v>
+      </c>
+      <c r="K18" s="2">
+        <v>91.549679747445879</v>
+      </c>
+      <c r="L18" s="2">
+        <v>59.590966556939073</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -2048,13 +3186,27 @@
         <f t="shared" si="0"/>
         <v>20.8</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="21">
+      <c r="G19" s="2">
+        <v>20.923020924635019</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.12302092463501779</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.9423564591269582</v>
+      </c>
+      <c r="K19" s="2">
+        <v>93.164293107877313</v>
+      </c>
+      <c r="L19" s="2">
+        <v>58.082468281430216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -2074,13 +3226,27 @@
         <f t="shared" si="0"/>
         <v>19.413333333333334</v>
       </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" ht="21">
+      <c r="G20" s="2">
+        <v>19.816754173666681</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.40342084033334658</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.97448156617286297</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.91004787693364109</v>
+      </c>
+      <c r="K20" s="2">
+        <v>93.338067341174721</v>
+      </c>
+      <c r="L20" s="2">
+        <v>55.978546026934083</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -2100,35 +3266,58 @@
         <f t="shared" si="0"/>
         <v>20.403333333333332</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="G21" s="2">
+        <v>20.149919172369319</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="1"/>
+        <v>0.25341416096401304</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.91050742926642803</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.85934101645521199</v>
+      </c>
+      <c r="K21" s="2">
+        <v>93.197609571201014</v>
+      </c>
+      <c r="L21" s="2">
+        <v>59.001658204694273</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H2:H21">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+      <formula>-0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" customWidth="1"/>
-    <col min="5" max="6" width="28.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" customWidth="1"/>
+    <col min="7" max="8" width="23.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.5546875" customWidth="1"/>
+    <col min="10" max="10" width="16.5546875" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2151,604 +3340,22 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>21.45</v>
-      </c>
-      <c r="D2" s="1">
-        <v>21.02</v>
-      </c>
-      <c r="E2" s="1">
-        <v>21.41</v>
-      </c>
-      <c r="F2" s="3">
-        <f>AVERAGE(C2:E2)</f>
-        <v>21.293333333333333</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="21">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1">
-        <v>20.62</v>
-      </c>
-      <c r="D3" s="1">
-        <v>21.58</v>
-      </c>
-      <c r="E3" s="1">
-        <v>20.77</v>
-      </c>
-      <c r="F3" s="3">
-        <f t="shared" ref="F3:F21" si="0">AVERAGE(C3:E3)</f>
-        <v>20.99</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="21">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="4">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4">
-        <v>27.21</v>
-      </c>
-      <c r="D4" s="4">
-        <v>27.06</v>
-      </c>
-      <c r="E4" s="4">
-        <v>27.68</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>27.316666666666663</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="21">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1">
-        <v>21.88</v>
-      </c>
-      <c r="D5" s="1">
-        <v>22.1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>22.29</v>
-      </c>
-      <c r="F5" s="3">
-        <f t="shared" si="0"/>
-        <v>22.090000000000003</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="21">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <v>22.23</v>
-      </c>
-      <c r="D6" s="1">
-        <v>22.22</v>
-      </c>
-      <c r="E6" s="1">
-        <v>22.58</v>
-      </c>
-      <c r="F6" s="3">
-        <f t="shared" si="0"/>
-        <v>22.343333333333334</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="21">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>21.47</v>
-      </c>
-      <c r="D7" s="1">
-        <v>21.38</v>
-      </c>
-      <c r="E7" s="1">
-        <v>21.7</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="0"/>
-        <v>21.516666666666666</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="21">
-      <c r="A8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="6">
-        <v>6</v>
-      </c>
-      <c r="C8" s="6">
-        <v>20.67</v>
-      </c>
-      <c r="D8" s="6">
-        <v>20.3</v>
-      </c>
-      <c r="E8" s="6">
-        <v>21.5</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" si="0"/>
-        <v>20.823333333333334</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="21">
-      <c r="A9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="8">
-        <v>6</v>
-      </c>
-      <c r="C9" s="8">
-        <v>22.15</v>
-      </c>
-      <c r="D9" s="8">
-        <v>22.18</v>
-      </c>
-      <c r="E9" s="8">
-        <v>22.62</v>
-      </c>
-      <c r="F9" s="9">
-        <f t="shared" si="0"/>
-        <v>22.316666666666666</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="21">
-      <c r="A10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="8">
-        <v>6</v>
-      </c>
-      <c r="C10" s="8">
-        <v>22.4</v>
-      </c>
-      <c r="D10" s="8">
-        <v>22.46</v>
-      </c>
-      <c r="E10" s="8">
-        <v>22.63</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="0"/>
-        <v>22.496666666666666</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="21">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1">
-        <v>21.39</v>
-      </c>
-      <c r="D11" s="1">
-        <v>20.92</v>
-      </c>
-      <c r="E11" s="1">
-        <v>21.44</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="0"/>
-        <v>21.25</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="21">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1">
-        <v>24.03</v>
-      </c>
-      <c r="D12" s="1">
-        <v>23.94</v>
-      </c>
-      <c r="E12" s="1">
-        <v>23.91</v>
-      </c>
-      <c r="F12" s="3">
-        <f t="shared" si="0"/>
-        <v>23.959999999999997</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="21">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1">
-        <v>21.43</v>
-      </c>
-      <c r="D13" s="1">
-        <v>21.18</v>
-      </c>
-      <c r="E13" s="1">
-        <v>21.35</v>
-      </c>
-      <c r="F13" s="3">
-        <f t="shared" si="0"/>
-        <v>21.32</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="21">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1">
-        <v>26.83</v>
-      </c>
-      <c r="D14" s="1">
-        <v>26.8</v>
-      </c>
-      <c r="E14" s="1">
-        <v>26.51</v>
-      </c>
-      <c r="F14" s="3">
-        <f t="shared" si="0"/>
-        <v>26.713333333333335</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="21">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1">
-        <v>21.27</v>
-      </c>
-      <c r="D15" s="1">
-        <v>21.24</v>
-      </c>
-      <c r="E15" s="1">
-        <v>21.88</v>
-      </c>
-      <c r="F15" s="3">
-        <f t="shared" si="0"/>
-        <v>21.463333333333335</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="21">
-      <c r="A16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="4">
-        <v>6</v>
-      </c>
-      <c r="C16" s="4">
-        <v>22.09</v>
-      </c>
-      <c r="D16" s="4">
-        <v>22.2</v>
-      </c>
-      <c r="E16" s="4">
-        <v>22.1</v>
-      </c>
-      <c r="F16" s="5">
-        <f t="shared" si="0"/>
-        <v>22.13</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="21">
-      <c r="A17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="4">
-        <v>6</v>
-      </c>
-      <c r="C17" s="4">
-        <v>23.13</v>
-      </c>
-      <c r="D17" s="4">
-        <v>23.16</v>
-      </c>
-      <c r="E17" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="F17" s="5">
-        <f t="shared" si="0"/>
-        <v>22.896666666666665</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="21">
-      <c r="A18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="4">
-        <v>6</v>
-      </c>
-      <c r="C18" s="4">
-        <v>20.93</v>
-      </c>
-      <c r="D18" s="4">
-        <v>21.08</v>
-      </c>
-      <c r="E18" s="4">
-        <v>21.13</v>
-      </c>
-      <c r="F18" s="5">
-        <f t="shared" si="0"/>
-        <v>21.046666666666667</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="21">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1">
-        <v>6</v>
-      </c>
-      <c r="C19" s="1">
-        <v>20.170000000000002</v>
-      </c>
-      <c r="D19" s="1">
-        <v>21.52</v>
-      </c>
-      <c r="E19" s="1">
-        <v>20.34</v>
-      </c>
-      <c r="F19" s="3">
-        <f t="shared" si="0"/>
-        <v>20.676666666666666</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="21">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1">
-        <v>20.059999999999999</v>
-      </c>
-      <c r="D20" s="1">
-        <v>22.18</v>
-      </c>
-      <c r="E20" s="1">
-        <v>21.72</v>
-      </c>
-      <c r="F20" s="3">
-        <f t="shared" si="0"/>
-        <v>21.319999999999997</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" ht="21">
-      <c r="A21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="6">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>20.420000000000002</v>
-      </c>
-      <c r="D21" s="6">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="E21" s="6">
-        <v>21.06</v>
-      </c>
-      <c r="F21" s="7">
-        <f t="shared" si="0"/>
-        <v>20.526666666666667</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="F22" s="10">
-        <f>AVERAGE(F2:F21)</f>
-        <v>22.224499999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="21">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="21">
+    <row r="2" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2768,13 +3375,27 @@
         <f>AVERAGE(C2:E2)</f>
         <v>23.25</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="21">
+      <c r="G2" s="1">
+        <v>20.2860449</v>
+      </c>
+      <c r="H2" s="2">
+        <f>F2-G2</f>
+        <v>2.9639550999999997</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.82416159700000002</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.69808773000000002</v>
+      </c>
+      <c r="K2" s="1">
+        <v>94.283380910000005</v>
+      </c>
+      <c r="L2" s="1">
+        <v>50.094762019999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2794,39 +3415,67 @@
         <f t="shared" ref="F3:F21" si="0">AVERAGE(C3:E3)</f>
         <v>21.176666666666666</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="21">
-      <c r="A4" s="6" t="s">
+      <c r="G3" s="1">
+        <v>20.459010889999998</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H21" si="1">F3-G3</f>
+        <v>0.71765577666666758</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.95263429399999999</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.84361923400000005</v>
+      </c>
+      <c r="K3" s="1">
+        <v>96.559285209999999</v>
+      </c>
+      <c r="L3" s="1">
+        <v>53.983678009999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="1">
         <v>6</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="1">
         <v>23.95</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="1">
         <v>23.86</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="1">
         <v>23.64</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
         <v>23.816666666666666</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="21">
+      <c r="G4" s="1">
+        <v>23.010214349999998</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="1"/>
+        <v>0.80645231666666817</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.93544584799999997</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.81470775699999998</v>
+      </c>
+      <c r="K4" s="1">
+        <v>97.853535230000006</v>
+      </c>
+      <c r="L4" s="1">
+        <v>54.434775080000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -2846,13 +3495,27 @@
         <f t="shared" si="0"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="21">
+      <c r="G5" s="1">
+        <v>21.324804310000001</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="1"/>
+        <v>0.52519568999999677</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.92785987400000003</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.836582469</v>
+      </c>
+      <c r="K5" s="1">
+        <v>96.751312209999995</v>
+      </c>
+      <c r="L5" s="1">
+        <v>54.406134729999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2872,13 +3535,27 @@
         <f t="shared" si="0"/>
         <v>20.249999999999996</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="21">
+      <c r="G6" s="1">
+        <v>19.549633310000001</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>0.70036668999999563</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.81375478599999995</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.97583407799999999</v>
+      </c>
+      <c r="K6" s="1">
+        <v>91.602384310000005</v>
+      </c>
+      <c r="L6" s="1">
+        <v>45.410714740000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2898,91 +3575,147 @@
         <f t="shared" si="0"/>
         <v>22.186666666666667</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="21">
-      <c r="A8" s="6" t="s">
+      <c r="G7" s="1">
+        <v>21.381426189999999</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="1"/>
+        <v>0.80524047666666831</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.808872272</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.84264150500000001</v>
+      </c>
+      <c r="K7" s="1">
+        <v>94.212338520000003</v>
+      </c>
+      <c r="L7" s="1">
+        <v>54.232816919999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="1">
         <v>27.54</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="1">
         <v>27.24</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="1">
         <v>27.53</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
         <v>27.436666666666667</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="21">
-      <c r="A9" s="6" t="s">
+      <c r="G8" s="1">
+        <v>26.286687919999999</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>1.1499787466666689</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.913327734</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.78772273299999995</v>
+      </c>
+      <c r="K8" s="1">
+        <v>98.171881369999994</v>
+      </c>
+      <c r="L8" s="1">
+        <v>53.150041569999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="1">
         <v>6</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="1">
         <v>22.4</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="1">
         <v>22.26</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="1">
         <v>22.48</v>
       </c>
       <c r="F9" s="3">
         <f t="shared" si="0"/>
         <v>22.38</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="21">
-      <c r="A10" s="6" t="s">
+      <c r="G9" s="1">
+        <v>23.233138749999998</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.85313874999999939</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.88651584500000002</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.86830382699999997</v>
+      </c>
+      <c r="K9" s="1">
+        <v>97.230023970000005</v>
+      </c>
+      <c r="L9" s="1">
+        <v>57.851259140000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="1">
         <v>20.57</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="1">
         <v>20.3</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="1">
         <v>20.89</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="0"/>
         <v>20.58666666666667</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="21">
+      <c r="G10" s="1">
+        <v>21.031468409999999</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.44480174333332911</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.97343241000000003</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.91333309699999998</v>
+      </c>
+      <c r="K10" s="1">
+        <v>86.888385880000001</v>
+      </c>
+      <c r="L10" s="1">
+        <v>54.06574011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -3002,13 +3735,27 @@
         <f t="shared" si="0"/>
         <v>22.333333333333332</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="21">
+      <c r="G11" s="1">
+        <v>20.868585840000001</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4647474933333307</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.93548933000000001</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.93290950800000005</v>
+      </c>
+      <c r="K11" s="1">
+        <v>96.081974470000006</v>
+      </c>
+      <c r="L11" s="1">
+        <v>51.357604639999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -3028,13 +3775,27 @@
         <f t="shared" si="0"/>
         <v>26.706666666666667</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="21">
+      <c r="G12" s="1">
+        <v>25.1936748</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="1"/>
+        <v>1.5129918666666669</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.95104708000000004</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.83762360300000005</v>
+      </c>
+      <c r="K12" s="1">
+        <v>94.398622169999996</v>
+      </c>
+      <c r="L12" s="1">
+        <v>59.149125060000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -3054,13 +3815,27 @@
         <f t="shared" si="0"/>
         <v>22.33666666666667</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="21">
+      <c r="G13" s="1">
+        <v>22.257442510000001</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>7.9224156666668932E-2</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.90245525000000004</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.84438961099999998</v>
+      </c>
+      <c r="K13" s="1">
+        <v>95.942443530000006</v>
+      </c>
+      <c r="L13" s="1">
+        <v>57.327574579999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -3080,13 +3855,27 @@
         <f t="shared" si="0"/>
         <v>21.193333333333332</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="21">
+      <c r="G14" s="1">
+        <v>22.460577839999999</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.2672445066666675</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.96268193199999996</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.96994490700000002</v>
+      </c>
+      <c r="K14" s="1">
+        <v>97.400812740000006</v>
+      </c>
+      <c r="L14" s="1">
+        <v>63.64850629</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -3106,91 +3895,147 @@
         <f t="shared" si="0"/>
         <v>21.983333333333334</v>
       </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="21">
-      <c r="A16" s="6" t="s">
+      <c r="G15" s="1">
+        <v>21.39481468</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>0.58851865333333464</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.804785525</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.87521082100000003</v>
+      </c>
+      <c r="K15" s="1">
+        <v>93.517786099999995</v>
+      </c>
+      <c r="L15" s="1">
+        <v>57.649419569999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="1">
         <v>6</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="1">
         <v>21</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="1">
         <v>21.16</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="1">
         <v>21.28</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="0"/>
         <v>21.146666666666665</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="21">
-      <c r="A17" s="6" t="s">
+      <c r="G16" s="1">
+        <v>21.273640990000001</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.1269743233333358</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.93462775099999995</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.94363894299999995</v>
+      </c>
+      <c r="K16" s="1">
+        <v>96.233003719999999</v>
+      </c>
+      <c r="L16" s="1">
+        <v>56.045636190000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="1">
         <v>6</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="1">
         <v>20.27</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="1">
         <v>19.98</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="1">
         <v>20.170000000000002</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" si="0"/>
         <v>20.14</v>
       </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="21">
-      <c r="A18" s="6" t="s">
+      <c r="G17" s="1">
+        <v>20.093785650000001</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="1"/>
+        <v>4.6214349999999627E-2</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.97234123900000002</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.91296734300000004</v>
+      </c>
+      <c r="K17" s="1">
+        <v>97.4348375</v>
+      </c>
+      <c r="L17" s="1">
+        <v>57.09325003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="1">
         <v>6</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="1">
         <v>21.25</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="1">
         <v>21.34</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="1">
         <v>21.52</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" si="0"/>
         <v>21.37</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="21">
+      <c r="G18" s="1">
+        <v>21.43158992</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="1"/>
+        <v>-6.158991999999941E-2</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.94276351899999999</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.88202524299999996</v>
+      </c>
+      <c r="K18" s="1">
+        <v>95.094437970000001</v>
+      </c>
+      <c r="L18" s="1">
+        <v>57.471416740000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -3210,13 +4055,27 @@
         <f t="shared" si="0"/>
         <v>21.64</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="21">
+      <c r="G19" s="1">
+        <v>21.52935012</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="1"/>
+        <v>0.11064988000000042</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.95000605900000001</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0.91284649900000003</v>
+      </c>
+      <c r="K19" s="1">
+        <v>96.595881840000004</v>
+      </c>
+      <c r="L19" s="1">
+        <v>58.309908290000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -3236,39 +4095,78 @@
         <f t="shared" si="0"/>
         <v>20.533333333333335</v>
       </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" ht="21">
-      <c r="A21" s="6" t="s">
+      <c r="G20" s="1">
+        <v>20.678665590000001</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="1"/>
+        <v>-0.14533225666666638</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.97390865900000001</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.93867543499999995</v>
+      </c>
+      <c r="K20" s="1">
+        <v>96.453924060000006</v>
+      </c>
+      <c r="L20" s="1">
+        <v>55.284376600000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="1">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="1">
         <v>20.82</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="1">
         <v>21.02</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="1">
         <v>21.05</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="0"/>
         <v>20.963333333333335</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="G21" s="1">
+        <v>20.194477320000001</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="1"/>
+        <v>0.76885601333333398</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.81724666000000001</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0.90649149900000003</v>
+      </c>
+      <c r="K21" s="1">
+        <v>88.084223559999998</v>
+      </c>
+      <c r="L21" s="1">
+        <v>51.468435360000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="H22" s="2"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H2:H21">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>-0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>